--- a/output/pms/Lập_trình_Python/Session 04 - Toán tử Số học, Toán tử So sánh và Toán tử Logic trong Python/Lesson 03 - Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán/Câu hỏi Quizz/Quizz_Session04_Lesson03.xlsx
+++ b/output/pms/Lập_trình_Python/Session 04 - Toán tử Số học, Toán tử So sánh và Toán tử Logic trong Python/Lesson 03 - Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán/Câu hỏi Quizz/Quizz_Session04_Lesson03.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Quizz Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quizz Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Khi triển khai Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán trong dự án `python`, cú pháp khai báo nào sau đây đúng quy chuẩn và đảm bảo chương trình biên dịch/thực thi không báo lỗi?</t>
+          <t>Thứ tự ưu tiên thực thi mặc định của các toán tử logic từ cao đến thấp trong Python là gì?</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -491,31 +491,31 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Khai báo cú pháp chuẩn theo quy ước đặt tên của `python`</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>and -&gt; or -&gt; not</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng từ khóa thuộc phiên bản đã bị loại bỏ (Deprecated)</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n"/>
+          <t>not -&gt; and -&gt; or</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bỏ qua việc khởi tạo giá trị ban đầu cho các tham số bắt buộc</t>
+          <t>or -&gt; and -&gt; not</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
@@ -525,7 +525,7 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Đặt tên biến bằng ký tự đặc biệt không được ngôn ngữ hỗ trợ</t>
+          <t>not -&gt; or -&gt; and</t>
         </is>
       </c>
       <c r="D5" s="3" t="n"/>
@@ -533,7 +533,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Trong cơ chế vận hành của Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán, luồng thực thi của hệ thống sẽ xử lý như thế nào khi gặp điều kiện rẽ nhánh trả về `False`?</t>
+          <t>Cho biểu thức logic: `res = True or False and False`. Giá trị của `res` là gì?</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Bỏ qua khối lệnh phụ thuộc và tiếp tục thực thi các câu lệnh kế tiếp</t>
+          <t>True</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -555,7 +555,7 @@
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Dừng toàn bộ hệ thống và thoát chương trình lập tức</t>
+          <t>False</t>
         </is>
       </c>
       <c r="D7" s="3" t="n"/>
@@ -565,7 +565,7 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Lặp lại khối lệnh vô tận cho đến khi bộ nhớ RAM bị tràn</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D8" s="3" t="n"/>
@@ -575,7 +575,7 @@
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Tự động sửa đổi giá trị dữ liệu đầu vào cho phù hợp</t>
+          <t>Lỗi SyntaxError</t>
         </is>
       </c>
       <c r="D9" s="3" t="n"/>
@@ -583,13 +583,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Cho đoạn mã nguồn minh họa Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán trong `python`:
-```python
-# Đoạn mã nguồn minh họa luồng xử lý
-result = process_data(input_val=100)
-print(result)
-```python
-Kết quả giá trị đầu ra nhận được là bao nhiêu khi dữ liệu đầu vào hợp lệ?</t>
+          <t>Cho đoạn mã Python sau: `x = 5; res = (x &gt; 3) and not (x == 5)`. Giá trị của `res` là bao nhiêu?</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -597,31 +591,31 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Giá trị được tính toán chính xác theo đúng nhánh rẽ được kích hoạt</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Giá trị mặc định ban đầu do biến không được cập nhật</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Báo lỗi Runtime Exception do truy cập biến chưa khởi tạo</t>
+          <t>None</t>
         </is>
       </c>
       <c r="D12" s="3" t="n"/>
@@ -631,7 +625,7 @@
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Trả về giá trị `None`/`null` do logic rẽ nhánh bị thiếu</t>
+          <t>Lỗi TypeError</t>
         </is>
       </c>
       <c r="D13" s="3" t="n"/>
@@ -639,7 +633,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Điểm khác biệt lớn nhất về tính ứng dụng giữa cấu trúc rẽ nhánh cơ bản và cấu trúc lồng nhau trong Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán là gì?</t>
+          <t>Biểu thức `res = False and (10 / 0 == 0)` có gây ra lỗi chia cho 0 (`ZeroDivisionError`) khi chạy không? Tại sao?</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -647,31 +641,31 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc lồng nhau cho phép kiểm tra thêm các điều kiện phụ thuộc khi điều kiện cha thỏa mãn</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>Có, vì Python tính toán mọi vế trong biểu thức logic trước khi trả về kết quả.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc rẽ nhánh cơ bản thực thi nhanh hơn gấp 10 lần cấu trúc lồng nhau</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n"/>
+          <t>Không, vì toán tử `and` gặp vế trái là `False` sẽ dừng đánh giá vế phải (cơ chế ngắn mạch).</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc lồng nhau chỉ dùng được cho kiểu dữ liệu chuỗi text</t>
+          <t>Có, vì phép so sánh `==` có độ ưu tiên cao hơn toán tử logic `and`.</t>
         </is>
       </c>
       <c r="D16" s="3" t="n"/>
@@ -681,7 +675,7 @@
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Cấu trúc rẽ nhánh cơ bản không cho phép sử dụng các toán tử so sánh</t>
+          <t>Không, vì Python tự động bỏ qua các lỗi chia cho 0 trong biểu thức so sánh.</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
@@ -689,7 +683,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Giả sử lập trình viên viết điều kiện trong Ứng dụng toán tử logic và Thứ tự ưu tiên tính toán nhưng quên không cập nhật biến đếm hoặc biến điều kiện trong thân khối lệnh. Bẫy lỗi (Pitfall) nào sẽ xảy ra?</t>
+          <t>Cho biểu thức `res = 3 + 2 * 4 &gt; 10`. Thứ tự ưu tiên tính toán của Python diễn ra thế nào?</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -697,31 +691,31 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Chương trình rơi vào bẫy lặp vô tận (Infinite Loop) hoặc kết quả bị treo</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
+          <t>Thực hiện phép so sánh `4 &gt; 10` trước, sau đó nhân với `2`, rồi cộng với `3`.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ngôn ngữ tự động bổ sung câu lệnh cập nhật biến ở background</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n"/>
+          <t>Thực hiện phép nhân `2 * 4`, tiếp theo cộng `3`, rồi mới so sánh `&gt; 10`.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Chương trình tự động bỏ qua khối lệnh và hoàn tất thực thi ngay</t>
+          <t>Thực hiện phép cộng `3 + 2`, tiếp theo nhân `4`, rồi mới so sánh `&gt; 10`.</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
@@ -731,7 +725,7 @@
       <c r="B21" s="4" t="n"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Hệ thống sẽ tự động chuyển đổi sang cấu trúc điều khiển khác</t>
+          <t>Thực hiện tuần tự từ trái qua phải: cộng `3+2`, nhân `4`, so sánh `&gt; 10`.</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
